--- a/data/processed/msft_info.xlsx
+++ b/data/processed/msft_info.xlsx
@@ -1239,7 +1239,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MSFTRatios" displayName="MSFTRatios" ref="A1:E7" headerRowCount="1">
   <autoFilter ref="A1:E7"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Microsoft Financial Ratios"/>
+    <tableColumn id="1" name="Ratios for Microsoft Inc."/>
     <tableColumn id="2" name="2022"/>
     <tableColumn id="3" name="2023"/>
     <tableColumn id="4" name="2024"/>
@@ -1833,7 +1833,7 @@
           <t>Overall Score</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="inlineStr">
         <is>
           <t>8.4/10</t>
@@ -2202,7 +2202,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Microsoft Financial Ratios</t>
+          <t>Ratios for Microsoft Inc.</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
